--- a/EngineeringBazar_Content_Template.xlsx
+++ b/EngineeringBazar_Content_Template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
   <si>
     <t>Products</t>
   </si>
@@ -150,13 +150,16 @@
     <t>coating=None; tolerance=+/-0.3mm</t>
   </si>
   <si>
+    <t>_</t>
+  </si>
+  <si>
     <t>per kg</t>
   </si>
   <si>
     <t>500 kg</t>
   </si>
   <si>
-    <t>Tata Steel</t>
+    <t>-</t>
   </si>
   <si>
     <t>Ready Stock (24–48h Dispatch)</t>
@@ -919,7 +922,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1539,17 +1542,17 @@
       <c r="N5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="O5" s="9">
-        <v>68.5</v>
+      <c r="O5" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="P5" s="9">
         <v>75</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S5" s="6">
         <v>4.5</v>
@@ -1558,13 +1561,13 @@
         <v>128</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V5" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W5" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X5" s="6" t="s">
         <v>36</v>
@@ -1573,7 +1576,7 @@
         <v>38</v>
       </c>
       <c r="Z5" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:26">
@@ -3330,7 +3333,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3348,7 +3351,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3361,39 +3364,39 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6">
       <c r="A5" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">

--- a/EngineeringBazar_Content_Template.xlsx
+++ b/EngineeringBazar_Content_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>Products</t>
   </si>
@@ -148,9 +148,6 @@
   </si>
   <si>
     <t>coating=None; tolerance=+/-0.3mm</t>
-  </si>
-  <si>
-    <t>_</t>
   </si>
   <si>
     <t>per kg</t>
@@ -1542,17 +1539,17 @@
       <c r="N5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="O5" s="9" t="s">
-        <v>40</v>
+      <c r="O5" s="9">
+        <v>25</v>
       </c>
       <c r="P5" s="9">
         <v>75</v>
       </c>
       <c r="Q5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="S5" s="6">
         <v>4.5</v>
@@ -1561,13 +1558,13 @@
         <v>128</v>
       </c>
       <c r="U5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="V5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="W5" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="W5" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="X5" s="6" t="s">
         <v>36</v>
@@ -1576,7 +1573,7 @@
         <v>38</v>
       </c>
       <c r="Z5" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:26">
@@ -3333,7 +3330,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3351,7 +3348,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3364,39 +3361,39 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6">
       <c r="A5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
